--- a/슈프리마_236200/data/슈프리마_데이터북_2026-10-26.xlsx
+++ b/슈프리마_236200/data/슈프리마_데이터북_2026-10-26.xlsx
@@ -22,6 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_규제타임라인" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_피어" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_DART접수번호" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_환원점검" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +49,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -75,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -83,6 +88,7 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -478,7 +484,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>시트: 01 연간실적 / 02 분기 / 03 PxQ(대수·대당매출·인력) / 04 인증수단 / 05 지역 / 06 현금·EV / 07 주주환원 / 08 주주구성 / 09 주가통계 / 10 환율 / 11 원가·마진 / 12 규제타임라인 / 13 피어 / 14 DART 접수번호</t>
+          <t>시트: 01 연간실적 / 02 분기 / 03 PxQ(대수·대당매출·인력) / 04 인증수단 / 05 지역 / 06 현금·EV / 07 주주환원 / 08 주주구성 / 09 주가통계 / 10 환율 / 11 원가·마진 / 12 규제타임라인 / 13 피어 / 14 DART 접수번호 / 15 환원점검(6장)</t>
         </is>
       </c>
     </row>
@@ -1610,6 +1616,751 @@
       <c r="B24" t="inlineStr">
         <is>
           <t>20260730900786</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>A. 약속 원문 [공시]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025.06.24 기업가치 제고 계획</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ROE 18%, 영상보안 진출·확대, PER 15배(2027 목표), IR 강화</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>20250624900365</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026.04.21 이행현황 + 주주환원 정책</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>주당 연간 최소 배당 400원(3년, 반기+결산), 3년 평균 총주주환원율 40%↑(연결 지배순이익 대비), 초과이익 시 특별배당 검토</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>20260421900639</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026.04.21 자사주 신탁</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>120억, 2026.04.21~2027.04.20, 종료 후 소각</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>20260421000337</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>공시 성격</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>자율공시(법적 구속력 없음). "향후 계획사항이 변경되거나 실제 결과가 예측정보와 다를 수 있음" 문구</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>B. 약속 vs 실행 (2026.10.26 현재)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>자사주 소각</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>282,962주(4.06%) 2026.02.05 소각</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>120억 신탁 매수</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7/20 기준 123,340주·57.5억(47.9%), 평균 46,617원</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>진행 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>최소 DPS 400원</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>반기 200원(13.7억) 2026.07.23 지급, 결산 200원 이상 남음</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>진행 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3년 평균 TSR 40%</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026E 신규 현금 환원 약 148억(배당 27.5 + 신탁 120) = 순이익 390~490억 대비 30~38%. 과거 취득분 소각 66억 포함 시 44~55%</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>산식 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>특별배당</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>자본준비금 100억 감액·이익잉여금 전입(2026.08.11). 사용 목적 미공시</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>준비 단계(추론)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ROE 18%(2027)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025 12.7%, 1Q26 13.0%</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>미달</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PER 15배(2027)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>현재 LTM 약 7배</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>미달</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IR 강화</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NDR 연 10회, 1:1 월 15회, 외국인 콜 월 1회, 2025 코스닥 공시우수법인</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>이행</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>C. 지배구조와 경제적 지분 [공시][신규]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>이재원 → 에이치큐</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>33.72%(3,306,595주)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>에이치큐 → 슈프리마</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>29.22%(2,037,843주)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>이재원 → 슈프리마(직접)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.16%(80,668주)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>특수관계인 합계(의결권)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>33.92%</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>이재원의 경제적 지분</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1.16% + 33.72%×29.22% = 11.0%</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>에이치큐 자체 금융자산</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1,254억(현금 524 + 기타유동 148 + 기타비유동 582, 2025말)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>20260319001168</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>에이치큐 시총 vs 보유 슈프리마 시가</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>약 1,274억 vs 약 1,072억</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>10/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>D. 이력 [공시][뉴스]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2015.12</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>인적분할(에이치큐/슈프리마), 이후 10년 슈프리마 배당 0원</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022~2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>슈프리마 자사주 신탁 30억(소각 없이 보유)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025.09.01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>에이치큐 자사주 657,491주(6.3%) 계열사 (유)벵가디아·임원 신동목에 장외 처분, 목적 "계열사간 협력"</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>20250901000506</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026.01.20</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>에이치큐 자사주 523,591주(4.99%) 숨마문화재단 무상 출연 공시</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026.01.19~02.10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>금감원 정정명령 3회(에이치큐 자기주식 처분 관련)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026.03.09~12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>출연 철회, 총 665,731주 소각 결정</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026.01.28</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>슈프리마 첫 소각(282,962주)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20260128900313</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026.04.21</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>지주·사업회사 동시 환원 정책(에이치큐: 최소 DPS 200원, 3년 평균 TSR 50%↑, 신탁 80억)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>20260421900413</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026.07.07</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>슈프리마 첫 배당(반기 200원)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20260707900461</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026.08.11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>독립이사 선임, 내부거래위원회 근거, 자본준비금 100억 감액</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20260811900687</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>E. 재원 시뮬레이션 (추정: 순이익=FCF=연 350억, 3년)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>환원율 40%</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3년 후 금융자산 약 2,821억</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>+630</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>환원율 60%</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>약 2,611억</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>환원율 100%</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>약 2,191억</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스트레스: 순이익 -30%(245억), 40%</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>약 2,632억</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>+441</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>F. 시장이 매긴 현금의 가치 (시총 3,599.5억, 금융자산 2,191억, LTM EBIT 351억)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>본업 EV/EBIT 6배</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>본업 2,106억 → 금융자산 평가 1,494억</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1원당 0.68원</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>본업 EV/EBIT 8배</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2,808억 → 792억</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0.36원</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>본업 EV/EBIT 10배</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>3,510억 → 90억</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.04원</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>본업 EV/EBIT 12배</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>4,212억 → -612억</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>음수</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>G. 이행 여부별 주당 가치 (예시, 비밸 확정 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>약속 파기(EV≈0, 2024년식)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>32,017원</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>현재</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>52,600원</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>이행(본업 8배 + 현금 80%)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>66,647원</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>+27%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>이행 + 리레이팅(10배 + 90%)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>80,107원</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>+52%</t>
         </is>
       </c>
     </row>

--- a/슈프리마_236200/data/슈프리마_데이터북_2026-10-26.xlsx
+++ b/슈프리마_236200/data/슈프리마_데이터북_2026-10-26.xlsx
@@ -23,6 +23,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_피어" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_DART접수번호" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_환원점검" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_부문해부" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_법인별매출" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_지역분기" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_수익인식_재고" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_Bull브리지" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,7 +60,7 @@
       <color rgb="00C00000"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +70,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007F7F7F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9F8BE"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -89,6 +99,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -485,6 +496,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>시트: 01 연간실적 / 02 분기 / 03 PxQ(대수·대당매출·인력) / 04 인증수단 / 05 지역 / 06 현금·EV / 07 주주환원 / 08 주주구성 / 09 주가통계 / 10 환율 / 11 원가·마진 / 12 규제타임라인 / 13 피어 / 14 DART 접수번호 / 15 환원점검(6장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-27 추가: 16 부문해부, 17 법인별매출, 18 지역분기, 19 수익인식·재고(데이터센터 정의 상충 포함), 20 Bull브리지(노란 칸 = 추정). 근거 문서: 07_매출구조_해부와_성장동력_2026-10-27.md</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2018,6 @@
           <t>인적분할(에이치큐/슈프리마), 이후 10년 슈프리마 배당 0원</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2013,7 +2030,6 @@
           <t>슈프리마 자사주 신탁 30억(소각 없이 보유)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2043,7 +2059,6 @@
           <t>에이치큐 자사주 523,591주(4.99%) 숨마문화재단 무상 출연 공시</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2056,7 +2071,6 @@
           <t>금감원 정정명령 3회(에이치큐 자기주식 처분 관련)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2069,7 +2083,6 @@
           <t>출연 철회, 총 665,731주 소각 결정</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2362,6 +2375,1609 @@
         <is>
           <t>+52%</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>[공시] 연결 매출실적(억원). 2020·2021은 2022 사업보고서 재분류값. 무엇을·누구에게·어떻게는 07 문서 2장</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>부문별 매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>부문</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1H25</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1H26</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2025 비중(%)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>25 YoY(%)</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1H YoY(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>통합보안시스템</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>414.68</v>
+      </c>
+      <c r="C5" t="n">
+        <v>556.25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>675.37</v>
+      </c>
+      <c r="E5" t="n">
+        <v>728.51</v>
+      </c>
+      <c r="F5" t="n">
+        <v>847.47</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1077.71</v>
+      </c>
+      <c r="H5" t="n">
+        <v>472.32</v>
+      </c>
+      <c r="I5" t="n">
+        <v>578.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>바이오인식솔루션</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>83.06</v>
+      </c>
+      <c r="C6" t="n">
+        <v>81.87</v>
+      </c>
+      <c r="D6" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="F6" t="n">
+        <v>123.45</v>
+      </c>
+      <c r="G6" t="n">
+        <v>144.22</v>
+      </c>
+      <c r="H6" t="n">
+        <v>80.33</v>
+      </c>
+      <c r="I6" t="n">
+        <v>76.73999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>용역</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="C7" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="D7" t="n">
+        <v>76.23999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>59.13</v>
+      </c>
+      <c r="F7" t="n">
+        <v>69.84</v>
+      </c>
+      <c r="G7" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="H7" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-17.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>45.92</v>
+      </c>
+      <c r="C8" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="D8" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="F8" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="G8" t="n">
+        <v>56.27</v>
+      </c>
+      <c r="H8" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="I8" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>577.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>725.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>894</v>
+      </c>
+      <c r="E9" t="n">
+        <v>946.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1082.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1373</v>
+      </c>
+      <c r="H9" t="n">
+        <v>613.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>714.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>100</v>
+      </c>
+      <c r="K9" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>내수/수출</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>부문</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2024 내수</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2024 수출</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2025 내수</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2025 수출</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1H25 내수</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1H25 수출</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1H26 내수</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1H26 수출</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2025 수출비중(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>통합보안시스템</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="C13" t="n">
+        <v>748.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>121.43</v>
+      </c>
+      <c r="E13" t="n">
+        <v>956.28</v>
+      </c>
+      <c r="F13" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="G13" t="n">
+        <v>425.17</v>
+      </c>
+      <c r="H13" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="I13" t="n">
+        <v>528.79</v>
+      </c>
+      <c r="J13" t="n">
+        <v>88.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>바이오인식솔루션</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="C14" t="n">
+        <v>117.68</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="E14" t="n">
+        <v>136.51</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="G14" t="n">
+        <v>75.27</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I14" t="n">
+        <v>74</v>
+      </c>
+      <c r="J14" t="n">
+        <v>94.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>용역</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>67.04000000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="F15" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="H15" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="D16" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>통합보안 P×Q(대당 매출 = 통합보안 매출 ÷ BioStar 생산대수, 만원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>생산대수</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>대당 매출(만원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>100850</v>
+      </c>
+      <c r="C20" t="n">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>126838</v>
+      </c>
+      <c r="C21" t="n">
+        <v>43.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>157908</v>
+      </c>
+      <c r="C22" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>152620</v>
+      </c>
+      <c r="C23" t="n">
+        <v>47.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>155754</v>
+      </c>
+      <c r="C24" t="n">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>176663</v>
+      </c>
+      <c r="C25" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1H25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>78238</v>
+      </c>
+      <c r="C26" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1H26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>102389</v>
+      </c>
+      <c r="C27" t="n">
+        <v>56.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>[공시] 법인 단독 매출(억원, 내부거래 제거 전) + 별도 특수관계자 주석의 본사→법인 매출. 법인 매출 급증에는 채널 이동(본사 직수출 → 법인 경유)이 섞여 있어 성장 지표로는 18번 시트의 연결 지역 매출을 쓴다</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>법인별 매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1H25</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1H26</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1H YoY(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>슈프리마(본사, 별도)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>677.98</v>
+      </c>
+      <c r="C5" t="n">
+        <v>855.74</v>
+      </c>
+      <c r="D5" t="n">
+        <v>889.67</v>
+      </c>
+      <c r="E5" t="n">
+        <v>995.48</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1232.64</v>
+      </c>
+      <c r="G5" t="n">
+        <v>547.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>620.79</v>
+      </c>
+      <c r="I5" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>79.03</v>
+      </c>
+      <c r="D6" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="E6" t="n">
+        <v>72.56999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>91.38</v>
+      </c>
+      <c r="G6" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="H6" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-8.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Europe SARL(프랑스)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>40.22</v>
+      </c>
+      <c r="C7" t="n">
+        <v>66.84</v>
+      </c>
+      <c r="D7" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="E7" t="n">
+        <v>127.91</v>
+      </c>
+      <c r="F7" t="n">
+        <v>148.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>77.58</v>
+      </c>
+      <c r="H7" t="n">
+        <v>77.70999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Middle East(두바이)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="F8" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="H8" t="n">
+        <v>98.84</v>
+      </c>
+      <c r="I8" t="n">
+        <v>442.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="C9" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="D9" t="n">
+        <v>46.22</v>
+      </c>
+      <c r="E9" t="n">
+        <v>46.63</v>
+      </c>
+      <c r="F9" t="n">
+        <v>62.88</v>
+      </c>
+      <c r="G9" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="H9" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="I9" t="n">
+        <v>79.90000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>America(미국)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="C10" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="D10" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="E10" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="F10" t="n">
+        <v>103.51</v>
+      </c>
+      <c r="G10" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>73.45</v>
+      </c>
+      <c r="I10" t="n">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Latam(멕시코)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="H11" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="I11" t="n">
+        <v>151.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="I12" t="n">
+        <v>83.59999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>연결 매출</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>725.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>894</v>
+      </c>
+      <c r="D13" t="n">
+        <v>946.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1082.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1373</v>
+      </c>
+      <c r="G13" t="n">
+        <v>613.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>714.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>본사 → 법인 매출(내부거래)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>법인</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2025 법인매출 ÷ 본사공급(배)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="C17" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Europe SARL(프랑스)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>110.89</v>
+      </c>
+      <c r="C18" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Middle East(두바이)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="C19" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="C20" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>America(미국)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="C21" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Latam(멕시코)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="C22" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>236.1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>343.1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>참고: 별도 기준 주요고객 A사 = Suprema Europe SARL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>연도</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>A사 매출(억)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Europe SARL 향 본사 매출(억)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>본사 매출 중 비중(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>110.89</v>
+      </c>
+      <c r="C28" t="n">
+        <v>110.89</v>
+      </c>
+      <c r="D28" t="n">
+        <v>11.14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="C29" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>[공시] 연결 부문별 정보 주석의 지역 매출(억원). 1Q = 1H - 2Q로 역산. 2Q26 아메리카 +72%는 1Q26 -19%와 함께 봐야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>지역별 매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>지역</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1H25</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1H26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2Q25</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2Q26</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1Q25</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1Q26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>209.46</v>
+      </c>
+      <c r="C5" t="n">
+        <v>265.61</v>
+      </c>
+      <c r="D5" t="n">
+        <v>105.01</v>
+      </c>
+      <c r="E5" t="n">
+        <v>108.47</v>
+      </c>
+      <c r="F5" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="G5" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="H5" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="I5" t="n">
+        <v>51.39</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>아시아</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>197.46</v>
+      </c>
+      <c r="C6" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>116.66</v>
+      </c>
+      <c r="E6" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="G6" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>47.18</v>
+      </c>
+      <c r="I6" t="n">
+        <v>81.77</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>아메리카</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>271.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>333.16</v>
+      </c>
+      <c r="D7" t="n">
+        <v>154.29</v>
+      </c>
+      <c r="E7" t="n">
+        <v>192.37</v>
+      </c>
+      <c r="F7" t="n">
+        <v>73.66</v>
+      </c>
+      <c r="G7" t="n">
+        <v>126.94</v>
+      </c>
+      <c r="H7" t="n">
+        <v>80.63</v>
+      </c>
+      <c r="I7" t="n">
+        <v>65.43000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>유럽</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>236.73</v>
+      </c>
+      <c r="C8" t="n">
+        <v>279.62</v>
+      </c>
+      <c r="D8" t="n">
+        <v>137.51</v>
+      </c>
+      <c r="E8" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="G8" t="n">
+        <v>70.76000000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>68.56</v>
+      </c>
+      <c r="I8" t="n">
+        <v>68.73999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>중동/아프리카</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>166.86</v>
+      </c>
+      <c r="C9" t="n">
+        <v>240.23</v>
+      </c>
+      <c r="D9" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="E9" t="n">
+        <v>109.58</v>
+      </c>
+      <c r="F9" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="G9" t="n">
+        <v>65.68000000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="I9" t="n">
+        <v>43.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1082.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1373</v>
+      </c>
+      <c r="D10" t="n">
+        <v>613.3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>714.6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>403.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>288</v>
+      </c>
+      <c r="I10" t="n">
+        <v>311.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>YoY(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>지역</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1H26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1Q26</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2Q26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>아시아</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>아메리카</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>유럽</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>중동/아프리카</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>44</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>31.4</v>
       </c>
     </row>
   </sheetData>
@@ -2695,6 +4311,1170 @@
       </c>
       <c r="H13" s="4" t="n">
         <v>11.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>[공시] 연결 수익 구분(억원), 재고자산(장부금액, 억원). 비재화(기간에 걸쳐 인식) 매출의 구성은 공시되지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>수익인식 시기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>한 시점(재화)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>기간에 걸쳐</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>기간에 걸쳐 비중(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>970.92</v>
+      </c>
+      <c r="C5" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1200.55</v>
+      </c>
+      <c r="C6" t="n">
+        <v>172.47</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1H25</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>535.23</v>
+      </c>
+      <c r="C7" t="n">
+        <v>78.06999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1H26</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>644.98</v>
+      </c>
+      <c r="C8" t="n">
+        <v>69.64</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>재화/기타 x 국내/해외</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>국내재화</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>해외재화</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>국내기타</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>해외기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>104.43</v>
+      </c>
+      <c r="C12" t="n">
+        <v>866.49</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10.65</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>171.43</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1029.13</v>
+      </c>
+      <c r="D13" t="n">
+        <v>92</v>
+      </c>
+      <c r="E13" t="n">
+        <v>80.47</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1H25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>461.73</v>
+      </c>
+      <c r="D14" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="E14" t="n">
+        <v>46.56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1H26</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>76.54000000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>568.4400000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="E15" t="n">
+        <v>37.69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>재고자산(연결)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>시점</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>제품</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>원재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="C19" t="n">
+        <v>105.41</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>111.89</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1H26</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="C21" t="n">
+        <v>195.23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>데이터센터 매출: 같은 기관 보고서끼리 정의가 다름(IR 확인 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1Q26</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IR협의회 2024.10 (E·D·C사 등 고객사 매출)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>40</v>
+      </c>
+      <c r="D25" t="n">
+        <v>62</v>
+      </c>
+      <c r="E25" t="n">
+        <v>65</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>80(E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IR협의회 2026.06 (데이터센터향 매출)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>25</v>
+      </c>
+      <c r="G26" t="n">
+        <v>31</v>
+      </c>
+      <c r="H26" t="n">
+        <v>26</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>70+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>(추정) SMIC 3팀 예시. 출발점 2025A: 대수 176,663 · 대당 61.0만원 · 얼굴 ASP 93.2만/지문 44.7만(IR협의회). 얼굴 비중 상승분은 지문에서 온다고 가정. 환율은 2025 평균 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Bull: 대수 +8%/년, 얼굴 57→62→67%, 시스템·SW 부착 +2%/년, 바이오 +3%, 용역 +10%, 기타 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>연도</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>대수(Q)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>얼굴 비중(%)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>믹스 반영 대당(만원)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>부착 반영 대당(만원)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>통합보안</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>바이오인식</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>용역</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>176663</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1077.7</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>190796</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1234.4</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1543.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>206060</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>68.51000000000001</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1411.8</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>153</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>1735.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>222545</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>68.28</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>72.45999999999999</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1612.5</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>157.6</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1952.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Blue-sky: 대수 +12%/년, 얼굴 60→68→75%, 부착 +3%/년, 바이오 +5%, 용역 +15%, 기타 +5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>연도</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>대수(Q)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>얼굴 비중(%)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>믹스 반영 대당(만원)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>부착 반영 대당(만원)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>통합보안</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>바이오인식</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>용역</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>176663</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>1077.7</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>197863</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>64.88</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>66.83</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1322.3</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>151.4</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1641.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>221606</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>72.95</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1616.6</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>159</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>1963.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>248199</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1957</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>167</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2333.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Bull 2025A→2028E 증가분 분해(억원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>요인</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>증가분</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>대수(Q) 증가</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>279.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>얼굴 믹스(P)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>161.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>시스템·SW 부착(P)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>바이오인식솔루션</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>용역(SI·설치)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>579.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>교차검증: 지역별로 쌓으면(연 성장 가정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>지역</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2025A</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>가정(연)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>265.61</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>290.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>아시아</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>439.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>아메리카</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>333.16</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>547.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>유럽</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>279.62</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>305.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>중동/아프리카</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>240.23</v>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>337.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>1373</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="6" t="n">
+        <v>1920.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>캐파 점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>1인 연간 생산능력(대)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Bull 2028E 필요 인원(가동률 95%)</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Blue-sky 2028E 필요 인원</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>1H26 인원</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>환율 민감도(번역 효과만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>2025 평균</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>1423.3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>1H26 평균</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>1485.4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>3Q26 평균</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>1417.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2026.10 평균</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>1337.3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2026.10 vs 2025 평균(%)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>번역 효과(수출비중 × 환율변화, %)</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>-4.9</v>
       </c>
     </row>
   </sheetData>

--- a/슈프리마_236200/data/슈프리마_데이터북_2026-10-26.xlsx
+++ b/슈프리마_236200/data/슈프리마_데이터북_2026-10-26.xlsx
@@ -28,6 +28,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_지역분기" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_수익인식_재고" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_Bull브리지" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_피어비교" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_NIST얼굴" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_규제타임라인v2" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_지정학수혜" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -503,6 +507,34 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>2026-10-27 추가: 16 부문해부, 17 법인별매출, 18 지역분기, 19 수익인식·재고(데이터센터 정의 상충 포함), 20 Bull브리지(노란 칸 = 추정). 근거 문서: 07_매출구조_해부와_성장동력_2026-10-27.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-27 추가(2): 21 피어비교, 22 NIST얼굴, 23 규제타임라인v2(12번 대체), 24 지정학수혜. 근거 문서: 08 피어·해자, 09 지정학</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-27 추가(2): 21 피어비교, 22 NIST얼굴, 23 규제타임라인v2(12번 대체), 24 지정학수혜. 근거 문서: 08 피어·해자, 09 지정학</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-27 추가(2): 21 피어비교, 22 NIST얼굴, 23 규제타임라인v2(12번 대체), 24 지정학수혜. 근거 문서: 08 피어·해자, 09 지정학</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-27 추가(2): 21 피어비교, 22 NIST얼굴, 23 규제타임라인v2(12번 대체), 24 지정학수혜. 근거 문서: 08 피어·해자, 09 지정학</t>
         </is>
       </c>
     </row>
@@ -5482,6 +5514,2470 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>[통계] stockanalysis.com(2026-10-26 종가, TTM). ZKTeco GPM은 2025 연보 계산값. 슈프리마 EV는 순현금 1,306억 기준(본서 정의 금융자산 2,191억이면 EV/EBIT 약 4배)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>피어 재무·밸류</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>회사</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>국가</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>그룹</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>매출(TTM, 현지통화)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>GPM(%)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>OPM(%)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>PER TTM</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>PER Fwd</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>EV/EBIT</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>배당(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>슈프리마</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>생체 출입통제</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KRW 147.4B</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ZKTeco(熵基科技)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>중국 출입통제</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CNY 2.30B</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hikvision</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>중국 영상·출입</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CNY 100.8B</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dahua</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>중국 영상·출입</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CNY 34.9B</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>14</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ASSA ABLOY(HID 모회사)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>글로벌 출입통제</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SEK 151.5B</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Allegion</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>글로벌 출입통제</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>USD 4.39B</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dormakaba</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>글로벌 출입통제</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CHF 2.79B</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Nedap</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>출입통제 SW 등</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EUR 297M</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>74</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>한화비전</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>국내 보안(영상)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>KRW 1.87T</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>17</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>아이디스</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>국내 보안(영상)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>KRW 329.5B</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>에스원</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>국내 보안(서비스)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>KRW 2.88T</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>유니온바이오메트릭스</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>국내 생체 출입통제</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>KRW 51.9B</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>ZKTeco 2025 연보 [공시(深交所)], 백만 위안</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2132.8</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>+7.1%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>해외 1,609.2(75.5%), 국내 523.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>출입통제(门禁) 제품</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1051.4</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>+10.2%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>GPM 51.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>근태(考勤) 제품</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>GPM 60.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>생체인식 센서</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>GPM 56.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GPM 전체 / 해외 / 국내</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>50.1% / 56.5% / 30.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>순이익(지배)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>214.7</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>+17.3%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>순이익률 10.1%, ROE 6.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>-14.3%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>매출의 8.7%, 연구인력 951명(-15%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>특허</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1,193건(발명 220)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>둥관 본사 + 태국(Armatura Tech) + 미국 공장 건설 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>주요 수출국(상장 당시)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>미국·멕시코·인도·UAE·사우디·인도네시아. 미국 = 해외매출의 18.2%(2021, 1.81억 위안)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>슈프리마 vs ZKTeco</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>슈프리마</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>ZKTeco</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>차이</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>매출(억원)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1373</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>약 4,220(×198원)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>약 3.1배</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>출입통제 매출(억원)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1078</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>약 2,080</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>약 1.9배</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GPM(%)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="C35" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>+16.0%p</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>해외 GPM(%)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>66(전사)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>+9.6%p</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>순이익률(%)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C37" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>+13.5%p</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>R&amp;D/매출(%)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>+1.3%p</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>같은 소매점 가격 사다리 [웹, 참고용]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>소매점</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>제품</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>통화</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>ZKTeco=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>UAE Neotech</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ZKTeco SpeedFace-V5L</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1780</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>UAE Neotech</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Suprema FaceStation</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>UAE Neotech</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>IDEMIA VisionPass</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5740</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>[통계] NIST FRTE 1:1 검증, 개발사별 최고 알고리즘 표(pages.nist.gov/frvt/html/frvt11.html, 2026-10-27). 값 = 오거부율(FNMR, 낮을수록 좋음), 괄호 = 순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>참가 개발사 수와 1위 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Mugshot</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Mugshot 12년+</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Visa-Border</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Border-Border</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>참가 수</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>441</v>
+      </c>
+      <c r="C5" t="n">
+        <v>441</v>
+      </c>
+      <c r="D5" t="n">
+        <v>442</v>
+      </c>
+      <c r="E5" t="n">
+        <v>277</v>
+      </c>
+      <c r="F5" t="n">
+        <v>442</v>
+      </c>
+      <c r="G5" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1위 FNMR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>주요 개발사</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>개발사</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>최근 제출</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Mugshot</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Mugshot 12년+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Visa-Border</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Border-Border</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Suprema AI(KR)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.0034 (180위)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.0031 (102위)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0026 (66위)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.0155 (69위)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.0050 (40위)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0520 (58위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Idemia(FR)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.0022 (23위)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.0020 (3위)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0020 (20위)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0055 (12위)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.0040 (20위)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0400 (14위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dahua(CN)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2021-12-20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.0026 (98위)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.0032 (105위)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.0033 (110위)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.0060 (56위)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0596 (82위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hikvision(CN)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.0093 (305위)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.0164 (322위)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.0108 (259위)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.0920 (240위)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Samsung S1(KR)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.0023 (49위)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.0023 (33위)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.0022 (30위)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.0078 (20위)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.0043 (26위)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.0438 (28위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cubox(KR)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.0025 (81위)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.0027 (69위)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.0023 (40위)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.0120 (46위)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.0044 (29위)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.0423 (20위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Alchera(KR)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2023-01-04</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.0026 (89위)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.0030 (90위)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.0025 (55위)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.0176 (79위)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0055 (49위)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.0492 (45위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Paravision(US)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.0020 (2위)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.0019 (2위)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.0015 (5위)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.0035 (3위)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.0032 (7위)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.0369 (6위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Suprema ID(KR, 분사)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2022-06-24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.0044 (219위)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.0062 (223위)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.0072 (215위)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.0229 (177위)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.1932 (194위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>슈프리마 백분위(상위 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Mugshot</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Mugshot 12년+</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Visa-Border</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Border-Border</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Kiosk</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>상위 %</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>[공시·뉴스] 1차 문서 확인: FCC DA 26-635·FCC 26-50(Federal Register 2026-13518, 2026-18535), FCC 22-84. 나머지는 언론 보도. 12번 시트를 대체</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>국가별 중국 보안장비 규제</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>국가</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>조치</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>범위</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2019-08-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NDAA §889(A)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>연방기관의 Hikvision·Dahua·Hytera 영상감시·통신장비 조달 금지(2020-08-13 (B) 계약자 사용 금지)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>정부·조달</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>공시된 법</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>상무부 Entity List</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Hikvision·Dahua 등 8개 중국 AI·감시업체 등재(미국산 부품 수출 통제)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>공급망</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FCC Covered List</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Hikvision·Dahua 영상감시·통신장비(공공안전·정부시설·핵심기반시설·국가안보 용도) 등재</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>전 시장(용도 기준)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2022-11-25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FCC 22-84</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Covered 장비 신규 인증 금지(2023-02-06 이후)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>신규 모델</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2022-11-24</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>영국</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>내각사무처 지시</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>중국 국가정보법 적용 기업 장비의 민감 정부시설 신규 설치 중단</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>정부 민감시설</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>호주</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>정부 감사·철거</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>정부 건물 250여 곳의 Hikvision·Dahua 장비 913대(카메라·인터콤·전자출입장치·녹화기) 철거</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>정부시설</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>인도</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MeitY CCTV 필수요건</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SoC 원산지 신고·소스코드 시험(STQC). 2025-04-09 시행, 2026-04-01 전면 적용(보도)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CCTV 전체</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>확정(출입단말은 대상 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>군 합동점검</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>국산으로 위장된 중국산 CCTV 1,300여 대 적발·철거</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>군</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>캐나다</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>투자법 국가안보 심사</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hikvision Canada 영업 중지 명령, 연방기관 구매·사용 금지</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>전 시장</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>하원 중국특위 서한</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FBI 인증 생체 스캐너 목록의 중국 기업 32곳 재검토 요구</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>생체인식</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>요구(미결)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RED 사이버보안 위임규정</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>무선기기 사이버보안 의무화. 동사 얼굴 단말 업계 최초 인증(2025-07)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>전 시장</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한국전력</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>변전소 등 중국산 CCTV 3,663대 2029년까지 교체</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>에너지</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>사이버보안법 개정안</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>18개 핵심 분야에서 고위험 공급자 장비 단계적 퇴출(국가 미지정)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>핵심 분야</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>입법 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>대만</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>경찰청</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ZKTeco 장비를 재포장했다는 의혹(Armatura, ZKTeco 지분 99.98%)으로 생체 근태 시스템 사용 중단</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>공공</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>확정(조사 중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FCC DA 26-635</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2022년 이전 인증된 Hikvision·Dahua 등 기존 모델까지 수입·판매 금지(공공안전·정부시설·국가안보 용도)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>기존 모델</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FCC 26-50(3차 R&amp;O)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>핵심기반시설 정의 채택(16개 섹터) → 핵심기반시설 보안용 수입·판매 금지 발효, Covered 기업 부품을 쓴 기기 인증 금지, 온라인몰 FCC ID 표시</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>핵심기반시설·부품</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>확정(10/13 시행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>국정감사</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>군 운용 중국산 CCTV 약 1,070대(Hikvision·Dahua·Uniview) 확인, 육군 2025년부터 보안기능 인증 제품만 도입</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>군</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>진행</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>(추정) 수혜 시나리오, 억원/연. T1·T2는 Bull 브리지(07 문서)의 아메리카 연 18% 가정 안에 이미 들어 있고, T3·T4는 브리지 밖 옵션</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>수혜 층위</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>층위</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>하단</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>상단</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>T1 미국 공공·핵심기반시설(Hik·Dahua 공백)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>동사 아메리카 333억 중 미국·캐나다 정부·데이터센터·에너지·금융. 2019~22년에 대부분 반영됐고 2026.07/10 확대분만 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>T2 캐나다·영국·호주·대만·한국 공공</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>확정·진행</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Hikvision Canada 철수, 대만 ZKTeco 재포장 사건, 한국 공공 CCTV 교체(AI 카메라·BioStar X 번들)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>T3 ZKTeco 규제 확대(옵션)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>미발생</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>ZKTeco 미국 매출 약 1.8억 위안(약 360억원, 2021) 중 20~50%가 비중국으로 이동, 동사 점유 1/3~1/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>T4 인도 CCTV 공백(옵션)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>미발생</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>인도 CCTV 시장 35억 달러(2024) 중 Hik·Dahua 30%. 동사 AI 카메라(2H26 출시 예정)가 STQC 인증을 받아 0.5%를 가져가면 약 250억</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>하단</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>상단</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>확정·진행(T1+T2)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>옵션(T3+T4)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>340</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
